--- a/Hand_edited_log/1/student/dungdvhe181404/TC5/GradeDetail.xlsx
+++ b/Hand_edited_log/1/student/dungdvhe181404/TC5/GradeDetail.xlsx
@@ -1050,10 +1050,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P2" s="0">
-        <x:v>62921</x:v>
+        <x:v>51754</x:v>
       </x:c>
       <x:c r="Q2" s="0">
-        <x:v>4002</x:v>
+        <x:v>4001</x:v>
       </x:c>
       <x:c r="R2" s="2" t="s">
         <x:v>46</x:v>
@@ -1106,10 +1106,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P3" s="0">
-        <x:v>4002</x:v>
+        <x:v>4001</x:v>
       </x:c>
       <x:c r="Q3" s="0">
-        <x:v>62921</x:v>
+        <x:v>51754</x:v>
       </x:c>
       <x:c r="R3" s="2" t="s">
         <x:v>46</x:v>
@@ -1162,10 +1162,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P4" s="0">
-        <x:v>62921</x:v>
+        <x:v>51754</x:v>
       </x:c>
       <x:c r="Q4" s="0">
-        <x:v>4002</x:v>
+        <x:v>4001</x:v>
       </x:c>
       <x:c r="R4" s="2" t="s">
         <x:v>46</x:v>
@@ -1218,10 +1218,10 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="P5" s="0">
-        <x:v>62921</x:v>
+        <x:v>51754</x:v>
       </x:c>
       <x:c r="Q5" s="0">
-        <x:v>4002</x:v>
+        <x:v>4001</x:v>
       </x:c>
       <x:c r="R5" s="2" t="s">
         <x:v>46</x:v>
@@ -1274,10 +1274,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P6" s="0">
-        <x:v>4002</x:v>
+        <x:v>4001</x:v>
       </x:c>
       <x:c r="Q6" s="0">
-        <x:v>62921</x:v>
+        <x:v>51754</x:v>
       </x:c>
       <x:c r="R6" s="2" t="s">
         <x:v>46</x:v>
@@ -1330,10 +1330,10 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="P7" s="0">
-        <x:v>4002</x:v>
+        <x:v>4001</x:v>
       </x:c>
       <x:c r="Q7" s="0">
-        <x:v>62921</x:v>
+        <x:v>51754</x:v>
       </x:c>
       <x:c r="R7" s="2" t="s">
         <x:v>46</x:v>
@@ -1386,10 +1386,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P8" s="0">
-        <x:v>62921</x:v>
+        <x:v>51754</x:v>
       </x:c>
       <x:c r="Q8" s="0">
-        <x:v>4002</x:v>
+        <x:v>4001</x:v>
       </x:c>
       <x:c r="R8" s="2" t="s">
         <x:v>46</x:v>
@@ -1442,10 +1442,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P9" s="0">
-        <x:v>4002</x:v>
+        <x:v>4001</x:v>
       </x:c>
       <x:c r="Q9" s="0">
-        <x:v>62921</x:v>
+        <x:v>51754</x:v>
       </x:c>
       <x:c r="R9" s="3" t="s">
         <x:v>61</x:v>
@@ -1498,10 +1498,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P10" s="0">
-        <x:v>62921</x:v>
+        <x:v>51754</x:v>
       </x:c>
       <x:c r="Q10" s="0">
-        <x:v>4002</x:v>
+        <x:v>4001</x:v>
       </x:c>
       <x:c r="R10" s="3" t="s">
         <x:v>61</x:v>
@@ -1554,10 +1554,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P11" s="0">
-        <x:v>62921</x:v>
+        <x:v>51754</x:v>
       </x:c>
       <x:c r="Q11" s="0">
-        <x:v>4002</x:v>
+        <x:v>4001</x:v>
       </x:c>
       <x:c r="R11" s="3" t="s">
         <x:v>61</x:v>
@@ -1610,10 +1610,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P12" s="0">
-        <x:v>4002</x:v>
+        <x:v>4001</x:v>
       </x:c>
       <x:c r="Q12" s="0">
-        <x:v>62921</x:v>
+        <x:v>51754</x:v>
       </x:c>
       <x:c r="R12" s="3" t="s">
         <x:v>61</x:v>
